--- a/processo_2/synthetic_proposals/PROPOSTA_002/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_002/ficha_pontuacao.xlsx
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>5.5</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr"/>
     </row>
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>2.5</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G9" t="inlineStr"/>
     </row>
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
@@ -680,17 +680,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,17 +726,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -804,12 +804,12 @@
           <t>Revista Científica Avançada 1</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>9338-3853</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -821,11 +821,7 @@
           <t>Revista Científica Avançada 2</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>7798-1242</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -839,11 +835,7 @@
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
@@ -858,7 +850,7 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1017,7 +1009,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1040,7 +1032,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1109,7 +1101,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1134,7 +1126,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>19.5</v>
+        <v>15</v>
       </c>
       <c r="G34" t="inlineStr"/>
     </row>
@@ -1177,7 +1169,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1200,7 +1192,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1246,7 +1238,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1269,7 +1261,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1292,7 +1284,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1315,7 +1307,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1338,7 +1330,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1361,7 +1353,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1384,17 +1376,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
         <v>1.5</v>
       </c>
       <c r="F46" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="G46" t="inlineStr"/>
     </row>
@@ -1543,13 +1535,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
         <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G53" t="inlineStr"/>
     </row>
@@ -1602,17 +1594,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>5</v>
       </c>
       <c r="F56" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
@@ -1625,17 +1617,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G57" t="inlineStr"/>
     </row>
@@ -1671,7 +1663,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1694,17 +1686,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G60" t="inlineStr"/>
     </row>
@@ -1719,7 +1711,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="G61" t="inlineStr"/>
     </row>
@@ -1812,13 +1804,13 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
         <v>4</v>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G66" t="inlineStr"/>
     </row>
@@ -1858,13 +1850,13 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
@@ -1881,13 +1873,13 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G69" t="inlineStr"/>
     </row>
@@ -1902,7 +1894,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G70" t="inlineStr"/>
     </row>
@@ -1917,7 +1909,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G71" t="inlineStr"/>
     </row>
